--- a/parcourt.xlsx
+++ b/parcourt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\merlin\Documents\GitHub\Actuarial-Data-Science-SRM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E1C410C3-FD50-4241-90C6-2893E0846D9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84D76055-4049-45F6-AF0F-B0BAF01B6620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="147">
   <si>
     <r>
       <rPr>
@@ -1836,6 +1836,12 @@
   </si>
   <si>
     <t>Unsupervised Learning Techniques (10-15%)</t>
+  </si>
+  <si>
+    <t>Toal</t>
+  </si>
+  <si>
+    <t>Completed</t>
   </si>
 </sst>
 </file>
@@ -1982,12 +1988,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
@@ -1996,24 +1996,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -2029,6 +2011,30 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2301,7 +2307,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Table 1'!$G$9:$G$14</c:f>
+              <c:f>'Table 1'!$G$8:$G$13</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -2327,7 +2333,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Table 1'!$H$9:$H$14</c:f>
+              <c:f>'Table 1'!$H$8:$H$13</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="6"/>
@@ -3027,13 +3033,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>566736</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>152399</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>9524</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>247649</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -3349,95 +3355,121 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:H68"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.1640625" customWidth="1"/>
     <col min="2" max="2" width="51.5" customWidth="1"/>
     <col min="3" max="3" width="52.5" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" customWidth="1"/>
     <col min="7" max="7" width="39" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="7" t="s">
+    <row r="1" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="D1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F1" s="6" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="18" t="s">
+    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="10" t="s">
         <v>134</v>
       </c>
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="11"/>
       <c r="B3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="11"/>
+      <c r="B4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="12"/>
+      <c r="B5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="19"/>
-      <c r="B4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="19"/>
-      <c r="B5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="20"/>
-      <c r="B6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="10" t="s">
-        <v>135</v>
-      </c>
+      <c r="F6" s="8">
+        <f>E6/D6</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="14"/>
       <c r="B7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7" s="16">
-        <f>E7/D7</f>
-        <v>0.5</v>
+        <v>1</v>
+      </c>
+      <c r="F7" s="8">
+        <f t="shared" ref="F7:F67" si="0">E7/D7</f>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="5"/>
+      <c r="A8" s="14"/>
       <c r="B8" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -3445,175 +3477,172 @@
       <c r="E8">
         <v>1</v>
       </c>
-      <c r="F8" s="16">
-        <f t="shared" ref="F8:F68" si="0">E8/D8</f>
+      <c r="F8" s="8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
+      <c r="G8" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="H8" s="9">
+        <f>100-(SUM(E6:E67)/SUM(D6:D67))*100</f>
+        <v>95.488721804511272</v>
+      </c>
     </row>
     <row r="9" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="5"/>
+      <c r="A9" s="14"/>
       <c r="B9" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9" s="8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="E9">
+      <c r="G9" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="H9" s="9">
+        <f>(SUM(E6:E17)/SUM(D6:D67))*100</f>
+        <v>4.5112781954887211</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="14"/>
+      <c r="B10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10">
         <v>1</v>
       </c>
-      <c r="F9" s="16">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="H9" s="17">
-        <f>100-(SUM(E7:E68)/SUM(D7:D68))*100</f>
-        <v>95.488721804511272</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="5"/>
-      <c r="B10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10">
-        <v>2</v>
-      </c>
-      <c r="E10">
-        <v>2</v>
-      </c>
-      <c r="F10" s="16">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="H10" s="17">
-        <f>(SUM(E7:E18)/SUM(D7:D68))*100</f>
-        <v>4.5112781954887211</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="5"/>
+      <c r="F10" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="H10" s="9">
+        <f>SUM(E18:E43)*100/SUM(D6:D67)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="14"/>
       <c r="B11" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
-      <c r="F11" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="H11" s="17">
-        <f>SUM(E19:E44)*100/SUM(D7:D68)</f>
+      <c r="F11" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="H11" s="9">
+        <f>SUM(E44:E52)*100/SUM(D6:D67)</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="5"/>
+      <c r="A12" s="14"/>
       <c r="B12" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="F12" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="H12" s="17">
-        <f>SUM(E45:E53)*100/SUM(D7:D68)</f>
+        <v>2</v>
+      </c>
+      <c r="F12" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="H12" s="9">
+        <f>SUM(E53:E61)*100/SUM(D6:D67)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="5"/>
+      <c r="A13" s="14"/>
       <c r="B13" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="D13">
         <v>2</v>
       </c>
-      <c r="F13" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="H13" s="17">
-        <f>SUM(E54:E62)*100/SUM(D7:D68)</f>
+      <c r="F13" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H13" s="9">
+        <f>SUM(E62:E67)*100/SUM(D6:D67)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="5"/>
+      <c r="A14" s="14"/>
       <c r="B14" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D14">
         <v>2</v>
       </c>
-      <c r="F14" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="H14" s="17">
-        <f>SUM(E63:E68)*100/SUM(D7:D68)</f>
+      <c r="F14" s="8">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="5"/>
+      <c r="A15" s="14"/>
       <c r="B15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="D15">
-        <v>2</v>
-      </c>
-      <c r="F15" s="16">
+        <v>1</v>
+      </c>
+      <c r="F15" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="5"/>
+      <c r="A16" s="14"/>
       <c r="B16" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>29</v>
@@ -3621,629 +3650,629 @@
       <c r="D16">
         <v>1</v>
       </c>
-      <c r="F16" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="5"/>
+      <c r="F16" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="14"/>
       <c r="B17" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="F17" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="5"/>
+        <v>2</v>
+      </c>
+      <c r="F17" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="13" t="s">
+        <v>136</v>
+      </c>
       <c r="B18" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D18">
+        <v>4</v>
+      </c>
+      <c r="F18" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="15"/>
+      <c r="B19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19">
         <v>2</v>
       </c>
-      <c r="F18" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D19">
-        <v>4</v>
-      </c>
-      <c r="F19" s="16">
+      <c r="F19" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="11"/>
+      <c r="A20" s="15"/>
       <c r="B20" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>38</v>
       </c>
       <c r="D20">
-        <v>2</v>
-      </c>
-      <c r="F20" s="16">
+        <v>5</v>
+      </c>
+      <c r="F20" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="11"/>
+      <c r="A21" s="15"/>
       <c r="B21" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D21">
-        <v>5</v>
-      </c>
-      <c r="F21" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="11"/>
+        <v>3</v>
+      </c>
+      <c r="F21" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="49.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="15"/>
       <c r="B22" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D22">
         <v>3</v>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="49.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="11"/>
+      <c r="A23" s="15"/>
       <c r="B23" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D23">
-        <v>3</v>
-      </c>
-      <c r="F23" s="16">
+        <v>5</v>
+      </c>
+      <c r="F23" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="49.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="11"/>
+      <c r="A24" s="15"/>
       <c r="B24" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D24">
+        <v>7</v>
+      </c>
+      <c r="F24" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="15"/>
+      <c r="B25" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D25">
         <v>5</v>
       </c>
-      <c r="F24" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="49.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="11"/>
-      <c r="B25" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D25">
-        <v>7</v>
-      </c>
-      <c r="F25" s="16">
+      <c r="F25" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="11"/>
+      <c r="A26" s="15"/>
       <c r="B26" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>50</v>
       </c>
       <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="F26" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="15"/>
+      <c r="B27" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D27">
+        <v>2</v>
+      </c>
+      <c r="F27" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="15"/>
+      <c r="B28" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D28">
         <v>5</v>
       </c>
-      <c r="F26" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="11"/>
-      <c r="B27" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D27">
-        <v>1</v>
-      </c>
-      <c r="F27" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="11"/>
-      <c r="B28" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D28">
+      <c r="F28" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="15"/>
+      <c r="B29" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D29">
         <v>2</v>
       </c>
-      <c r="F28" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="11"/>
-      <c r="B29" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D29">
-        <v>5</v>
-      </c>
-      <c r="F29" s="16">
+      <c r="F29" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="11"/>
+      <c r="A30" s="15"/>
       <c r="B30" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="D30">
         <v>2</v>
       </c>
-      <c r="F30" s="16">
+      <c r="F30" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="11"/>
+      <c r="A31" s="15"/>
       <c r="B31" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D31">
         <v>2</v>
       </c>
-      <c r="F31" s="16">
+      <c r="F31" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="11"/>
+      <c r="A32" s="15"/>
       <c r="B32" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D32">
         <v>2</v>
       </c>
-      <c r="F32" s="16">
+      <c r="F32" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="11"/>
+      <c r="A33" s="15"/>
       <c r="B33" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D33">
-        <v>2</v>
-      </c>
-      <c r="F33" s="16">
+        <v>1</v>
+      </c>
+      <c r="F33" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="11"/>
+      <c r="A34" s="15"/>
       <c r="B34" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D34">
         <v>1</v>
       </c>
-      <c r="F34" s="16">
+      <c r="F34" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="11"/>
+      <c r="A35" s="15"/>
       <c r="B35" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D35">
-        <v>1</v>
-      </c>
-      <c r="F35" s="16">
+        <v>2</v>
+      </c>
+      <c r="F35" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="11"/>
+      <c r="A36" s="15"/>
       <c r="B36" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>70</v>
       </c>
       <c r="D36">
         <v>2</v>
       </c>
-      <c r="F36" s="16">
+      <c r="F36" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="11"/>
+      <c r="A37" s="15"/>
       <c r="B37" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D37">
         <v>2</v>
       </c>
-      <c r="F37" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="11"/>
+      <c r="F37" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="49.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="15"/>
       <c r="B38" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D38">
-        <v>2</v>
-      </c>
-      <c r="F38" s="16">
+        <v>3</v>
+      </c>
+      <c r="F38" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="49.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="11"/>
+      <c r="A39" s="15"/>
       <c r="B39" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>76</v>
       </c>
       <c r="D39">
-        <v>3</v>
-      </c>
-      <c r="F39" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="49.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="11"/>
+        <v>1</v>
+      </c>
+      <c r="F39" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="15"/>
       <c r="B40" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D40">
         <v>1</v>
       </c>
-      <c r="F40" s="16">
+      <c r="F40" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="11"/>
+      <c r="A41" s="15"/>
       <c r="B41" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D41">
-        <v>1</v>
-      </c>
-      <c r="F41" s="16">
+        <v>2</v>
+      </c>
+      <c r="F41" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="11"/>
+      <c r="A42" s="15"/>
       <c r="B42" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D42">
+        <v>3</v>
+      </c>
+      <c r="F42" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="16"/>
+      <c r="B43" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D43">
         <v>2</v>
       </c>
-      <c r="F42" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="11"/>
-      <c r="B43" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D43">
+      <c r="F43" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D44">
         <v>3</v>
       </c>
-      <c r="F43" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="12"/>
-      <c r="B44" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D44">
-        <v>2</v>
-      </c>
-      <c r="F44" s="16">
+      <c r="F44" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="13" t="s">
-        <v>137</v>
-      </c>
+      <c r="A45" s="18"/>
       <c r="B45" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D45">
         <v>3</v>
       </c>
-      <c r="F45" s="16">
+      <c r="F45" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="14"/>
+      <c r="A46" s="18"/>
       <c r="B46" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D46">
-        <v>3</v>
-      </c>
-      <c r="F46" s="16">
+        <v>1</v>
+      </c>
+      <c r="F46" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="14"/>
+      <c r="A47" s="18"/>
       <c r="B47" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D47">
+        <v>4</v>
+      </c>
+      <c r="F47" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="18"/>
+      <c r="B48" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D48">
+        <v>2</v>
+      </c>
+      <c r="F48" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="18"/>
+      <c r="B49" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D49">
         <v>1</v>
       </c>
-      <c r="F47" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="14"/>
-      <c r="B48" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D48">
-        <v>4</v>
-      </c>
-      <c r="F48" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="14"/>
-      <c r="B49" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D49">
-        <v>2</v>
-      </c>
-      <c r="F49" s="16">
+      <c r="F49" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="14"/>
+      <c r="A50" s="18"/>
       <c r="B50" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D50">
         <v>1</v>
       </c>
-      <c r="F50" s="16">
+      <c r="F50" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="14"/>
+      <c r="A51" s="18"/>
       <c r="B51" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D51">
         <v>1</v>
       </c>
-      <c r="F51" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="14"/>
+      <c r="F51" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="19"/>
       <c r="B52" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D52">
-        <v>1</v>
-      </c>
-      <c r="F52" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="15"/>
+        <v>2</v>
+      </c>
+      <c r="F52" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="13" t="s">
+        <v>138</v>
+      </c>
       <c r="B53" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D53">
         <v>2</v>
       </c>
-      <c r="F53" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="10" t="s">
-        <v>138</v>
-      </c>
+      <c r="F53" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="14"/>
       <c r="B54" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D54">
-        <v>2</v>
-      </c>
-      <c r="F54" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="5"/>
+        <v>1</v>
+      </c>
+      <c r="F54" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="14"/>
       <c r="B55" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>106</v>
@@ -4251,15 +4280,15 @@
       <c r="D55">
         <v>1</v>
       </c>
-      <c r="F55" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="5"/>
+      <c r="F55" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="14"/>
       <c r="B56" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>106</v>
@@ -4267,215 +4296,199 @@
       <c r="D56">
         <v>1</v>
       </c>
-      <c r="F56" s="16">
+      <c r="F56" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="5"/>
+      <c r="A57" s="14"/>
       <c r="B57" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D57">
         <v>1</v>
       </c>
-      <c r="F57" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="5"/>
+      <c r="F57" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="14"/>
       <c r="B58" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D58">
+        <v>2</v>
+      </c>
+      <c r="F58" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="14"/>
+      <c r="B59" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D59">
         <v>1</v>
       </c>
-      <c r="F58" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="5"/>
-      <c r="B59" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D59">
-        <v>2</v>
-      </c>
-      <c r="F59" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="5"/>
+      <c r="F59" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="14"/>
       <c r="B60" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D60">
         <v>1</v>
       </c>
-      <c r="F60" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="5"/>
+      <c r="F60" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="20"/>
       <c r="B61" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D61">
         <v>1</v>
       </c>
-      <c r="F61" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="6"/>
+      <c r="F61" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="17" t="s">
+        <v>139</v>
+      </c>
       <c r="B62" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D62">
         <v>1</v>
       </c>
-      <c r="F62" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="13" t="s">
-        <v>139</v>
-      </c>
+      <c r="F62" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="18"/>
       <c r="B63" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D63">
+        <v>3</v>
+      </c>
+      <c r="F63" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="18"/>
+      <c r="B64" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D64">
+        <v>5</v>
+      </c>
+      <c r="F64" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="18"/>
+      <c r="B65" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D65">
+        <v>3</v>
+      </c>
+      <c r="F65" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="18"/>
+      <c r="B66" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D66">
         <v>1</v>
       </c>
-      <c r="F63" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="14"/>
-      <c r="B64" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D64">
-        <v>3</v>
-      </c>
-      <c r="F64" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="14"/>
-      <c r="B65" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="D65">
-        <v>5</v>
-      </c>
-      <c r="F65" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="14"/>
-      <c r="B66" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D66">
-        <v>3</v>
-      </c>
-      <c r="F66" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="14"/>
+      <c r="F66" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="19"/>
       <c r="B67" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D67">
         <v>1</v>
       </c>
-      <c r="F67" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="15"/>
-      <c r="B68" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D68">
-        <v>1</v>
-      </c>
-      <c r="F68" s="16">
+      <c r="F67" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A54:A62"/>
-    <mergeCell ref="A19:A44"/>
-    <mergeCell ref="A45:A53"/>
-    <mergeCell ref="A63:A68"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="A7:A18"/>
+    <mergeCell ref="A53:A61"/>
+    <mergeCell ref="A18:A43"/>
+    <mergeCell ref="A44:A52"/>
+    <mergeCell ref="A62:A67"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A17"/>
   </mergeCells>
-  <conditionalFormatting sqref="F7:F68">
+  <conditionalFormatting sqref="F6:F67">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>

--- a/parcourt.xlsx
+++ b/parcourt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\merlin\Documents\GitHub\Actuarial-Data-Science-SRM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84D76055-4049-45F6-AF0F-B0BAF01B6620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6F5797C-AAD0-478F-9A8C-21F325874AC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="1" r:id="rId1"/>
@@ -3526,6 +3526,9 @@
       <c r="D10">
         <v>1</v>
       </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
       <c r="F10" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3549,6 +3552,9 @@
       <c r="D11">
         <v>1</v>
       </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
       <c r="F11" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3572,6 +3578,9 @@
       <c r="D12">
         <v>2</v>
       </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
       <c r="F12" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3595,6 +3604,9 @@
       <c r="D13">
         <v>2</v>
       </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
       <c r="F13" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3618,6 +3630,9 @@
       <c r="D14">
         <v>2</v>
       </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
       <c r="F14" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3634,6 +3649,9 @@
       <c r="D15">
         <v>1</v>
       </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
       <c r="F15" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3650,6 +3668,9 @@
       <c r="D16">
         <v>1</v>
       </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
       <c r="F16" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3666,6 +3687,9 @@
       <c r="D17">
         <v>2</v>
       </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
       <c r="F17" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3683,6 +3707,9 @@
       </c>
       <c r="D18">
         <v>4</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
       </c>
       <c r="F18" s="8">
         <f t="shared" si="0"/>
@@ -3700,6 +3727,9 @@
       <c r="D19">
         <v>2</v>
       </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
       <c r="F19" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3716,6 +3746,9 @@
       <c r="D20">
         <v>5</v>
       </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
       <c r="F20" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3732,6 +3765,9 @@
       <c r="D21">
         <v>3</v>
       </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
       <c r="F21" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3748,6 +3784,9 @@
       <c r="D22">
         <v>3</v>
       </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
       <c r="F22" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3764,6 +3803,9 @@
       <c r="D23">
         <v>5</v>
       </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
       <c r="F23" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3780,6 +3822,9 @@
       <c r="D24">
         <v>7</v>
       </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
       <c r="F24" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3796,6 +3841,9 @@
       <c r="D25">
         <v>5</v>
       </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
       <c r="F25" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3812,6 +3860,9 @@
       <c r="D26">
         <v>1</v>
       </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
       <c r="F26" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3828,6 +3879,9 @@
       <c r="D27">
         <v>2</v>
       </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
       <c r="F27" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3844,6 +3898,9 @@
       <c r="D28">
         <v>5</v>
       </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
       <c r="F28" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3860,6 +3917,9 @@
       <c r="D29">
         <v>2</v>
       </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
       <c r="F29" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3876,6 +3936,9 @@
       <c r="D30">
         <v>2</v>
       </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
       <c r="F30" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3892,6 +3955,9 @@
       <c r="D31">
         <v>2</v>
       </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
       <c r="F31" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3908,6 +3974,9 @@
       <c r="D32">
         <v>2</v>
       </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
       <c r="F32" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3924,6 +3993,9 @@
       <c r="D33">
         <v>1</v>
       </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
       <c r="F33" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3940,6 +4012,9 @@
       <c r="D34">
         <v>1</v>
       </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
       <c r="F34" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3956,6 +4031,9 @@
       <c r="D35">
         <v>2</v>
       </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
       <c r="F35" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3972,6 +4050,9 @@
       <c r="D36">
         <v>2</v>
       </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
       <c r="F36" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3988,6 +4069,9 @@
       <c r="D37">
         <v>2</v>
       </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
       <c r="F37" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4004,6 +4088,9 @@
       <c r="D38">
         <v>3</v>
       </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
       <c r="F38" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4020,6 +4107,9 @@
       <c r="D39">
         <v>1</v>
       </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
       <c r="F39" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4036,6 +4126,9 @@
       <c r="D40">
         <v>1</v>
       </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
       <c r="F40" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4052,6 +4145,9 @@
       <c r="D41">
         <v>2</v>
       </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
       <c r="F41" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4068,6 +4164,9 @@
       <c r="D42">
         <v>3</v>
       </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
       <c r="F42" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4084,6 +4183,9 @@
       <c r="D43">
         <v>2</v>
       </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
       <c r="F43" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4101,6 +4203,9 @@
       </c>
       <c r="D44">
         <v>3</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
       </c>
       <c r="F44" s="8">
         <f t="shared" si="0"/>
@@ -4118,6 +4223,9 @@
       <c r="D45">
         <v>3</v>
       </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
       <c r="F45" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4134,6 +4242,9 @@
       <c r="D46">
         <v>1</v>
       </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
       <c r="F46" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4150,6 +4261,9 @@
       <c r="D47">
         <v>4</v>
       </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
       <c r="F47" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4166,6 +4280,9 @@
       <c r="D48">
         <v>2</v>
       </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
       <c r="F48" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4182,6 +4299,9 @@
       <c r="D49">
         <v>1</v>
       </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
       <c r="F49" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4198,6 +4318,9 @@
       <c r="D50">
         <v>1</v>
       </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
       <c r="F50" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4214,6 +4337,9 @@
       <c r="D51">
         <v>1</v>
       </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
       <c r="F51" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4230,6 +4356,9 @@
       <c r="D52">
         <v>2</v>
       </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
       <c r="F52" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4247,6 +4376,9 @@
       </c>
       <c r="D53">
         <v>2</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
       </c>
       <c r="F53" s="8">
         <f t="shared" si="0"/>
@@ -4264,6 +4396,9 @@
       <c r="D54">
         <v>1</v>
       </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
       <c r="F54" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4280,6 +4415,9 @@
       <c r="D55">
         <v>1</v>
       </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
       <c r="F55" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4296,6 +4434,9 @@
       <c r="D56">
         <v>1</v>
       </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
       <c r="F56" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4312,6 +4453,9 @@
       <c r="D57">
         <v>1</v>
       </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
       <c r="F57" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4328,6 +4472,9 @@
       <c r="D58">
         <v>2</v>
       </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
       <c r="F58" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4344,6 +4491,9 @@
       <c r="D59">
         <v>1</v>
       </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
       <c r="F59" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4360,6 +4510,9 @@
       <c r="D60">
         <v>1</v>
       </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
       <c r="F60" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4376,6 +4529,9 @@
       <c r="D61">
         <v>1</v>
       </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
       <c r="F61" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4393,6 +4549,9 @@
       </c>
       <c r="D62">
         <v>1</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
       </c>
       <c r="F62" s="8">
         <f t="shared" si="0"/>
@@ -4410,6 +4569,9 @@
       <c r="D63">
         <v>3</v>
       </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
       <c r="F63" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4426,6 +4588,9 @@
       <c r="D64">
         <v>5</v>
       </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
       <c r="F64" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4442,6 +4607,9 @@
       <c r="D65">
         <v>3</v>
       </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
       <c r="F65" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4458,6 +4626,9 @@
       <c r="D66">
         <v>1</v>
       </c>
+      <c r="E66">
+        <v>0</v>
+      </c>
       <c r="F66" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4473,6 +4644,9 @@
       </c>
       <c r="D67">
         <v>1</v>
+      </c>
+      <c r="E67">
+        <v>0</v>
       </c>
       <c r="F67" s="8">
         <f t="shared" si="0"/>
